--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,9 +780,437 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136530942</v>
+      </c>
+      <c r="B3" t="n">
+        <v>108437</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Z969 Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>557694</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7033606</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136530942</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136531599</v>
+      </c>
+      <c r="B4" t="n">
+        <v>108437</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220102</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kärrfibbla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crepis paludosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Z969 Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>557534</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7033569</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136531599</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136534941</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103919</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222004</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kärrviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Viola palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Z969 Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>557696</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7033597</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136534941</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136545476</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101442</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Z969 Ramsele, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>557677</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7033604</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136545476</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103919</v>
+        <v>103922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101442</v>
+        <v>101445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103922</v>
+        <v>103923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101445</v>
+        <v>101446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103923</v>
+        <v>103928</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101446</v>
+        <v>101451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108446</v>
+        <v>108448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103928</v>
+        <v>103930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101451</v>
+        <v>101453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Björn Almkvist</t>
+          <t>Björn Almkvist, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108448</v>
+        <v>108454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103930</v>
+        <v>103936</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101453</v>
+        <v>101459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108454</v>
+        <v>108456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103936</v>
+        <v>103938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108456</v>
+        <v>108457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103938</v>
+        <v>103939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Björn Almkvist, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Björn Almkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101461</v>
+        <v>101462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108457</v>
+        <v>108463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103939</v>
+        <v>103945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101462</v>
+        <v>101468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108463</v>
+        <v>108467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103945</v>
+        <v>103949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101468</v>
+        <v>101472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108467</v>
+        <v>108469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101472</v>
+        <v>101474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108469</v>
+        <v>108471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101474</v>
+        <v>101476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108471</v>
+        <v>108484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103953</v>
+        <v>103966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101476</v>
+        <v>101489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 5033-2024 artfynd.xlsx
+++ b/artfynd/A 5033-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136530942</v>
       </c>
       <c r="B3" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>136531599</v>
       </c>
       <c r="B4" t="n">
-        <v>108484</v>
+        <v>108486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>136534941</v>
       </c>
       <c r="B5" t="n">
-        <v>103966</v>
+        <v>103968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136545476</v>
       </c>
       <c r="B6" t="n">
-        <v>101489</v>
+        <v>101491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
